--- a/data/trans_orig/P6905-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P6905-Estudios-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si su trabajo le afecta de manera que tiene dolores de cabeza en 2007</t>
+          <t>Población según si su trabajo le afecta de manera que tiene dolores de cabeza en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>21743</t>
+          <t>21642</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>41407</t>
+          <t>40788</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>19,54%</t>
+          <t>19,45%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>37,21%</t>
+          <t>36,65%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4049</t>
+          <t>3933</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>14285</t>
+          <t>13915</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10,78%</t>
+          <t>10,47%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>38,02%</t>
+          <t>37,04%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>28563</t>
+          <t>28910</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>51172</t>
+          <t>51329</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>19,19%</t>
+          <t>19,42%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>34,38%</t>
+          <t>34,48%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>69879</t>
+          <t>70498</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>89543</t>
+          <t>89644</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>62,79%</t>
+          <t>63,35%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>80,46%</t>
+          <t>80,55%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>23283</t>
+          <t>23653</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>33519</t>
+          <t>33635</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>61,98%</t>
+          <t>62,96%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>89,22%</t>
+          <t>89,53%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>97682</t>
+          <t>97525</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>120291</t>
+          <t>119944</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>65,62%</t>
+          <t>65,52%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>80,81%</t>
+          <t>80,58%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>69675</t>
+          <t>69403</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>101804</t>
+          <t>101999</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>24,28%</t>
+          <t>24,19%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>35,48%</t>
+          <t>35,55%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>46125</t>
+          <t>44806</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>68487</t>
+          <t>66656</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>38,9%</t>
+          <t>37,79%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>57,76%</t>
+          <t>56,22%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>121332</t>
+          <t>122791</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>160564</t>
+          <t>160636</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>29,92%</t>
+          <t>30,28%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>39,6%</t>
+          <t>39,61%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>185141</t>
+          <t>184946</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>217270</t>
+          <t>217542</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>64,52%</t>
+          <t>64,45%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>75,72%</t>
+          <t>75,81%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>50084</t>
+          <t>51915</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>72446</t>
+          <t>73765</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>42,24%</t>
+          <t>43,78%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>61,1%</t>
+          <t>62,21%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>244951</t>
+          <t>244879</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>284183</t>
+          <t>282724</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>60,4%</t>
+          <t>60,39%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>70,08%</t>
+          <t>69,72%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>19264</t>
+          <t>18674</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>35563</t>
+          <t>35100</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>26,01%</t>
+          <t>25,21%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>48,01%</t>
+          <t>47,38%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>17836</t>
+          <t>16839</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>33619</t>
+          <t>33195</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>27,88%</t>
+          <t>26,32%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>52,54%</t>
+          <t>51,88%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>40619</t>
+          <t>40270</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>63228</t>
+          <t>63964</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>29,42%</t>
+          <t>29,17%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>45,8%</t>
+          <t>46,33%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>38512</t>
+          <t>38975</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>54811</t>
+          <t>55401</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>51,99%</t>
+          <t>52,62%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>73,99%</t>
+          <t>74,79%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>30364</t>
+          <t>30788</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>46147</t>
+          <t>47144</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>47,46%</t>
+          <t>48,12%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>72,12%</t>
+          <t>73,68%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>74830</t>
+          <t>74094</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>97439</t>
+          <t>97788</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>54,2%</t>
+          <t>53,67%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>70,58%</t>
+          <t>70,83%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>120280</t>
+          <t>123771</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>163652</t>
+          <t>166150</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>25,47%</t>
+          <t>26,21%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>34,65%</t>
+          <t>35,18%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>77154</t>
+          <t>76002</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>104241</t>
+          <t>104901</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>35,05%</t>
+          <t>34,53%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>47,36%</t>
+          <t>47,66%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>209046</t>
+          <t>204964</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>259159</t>
+          <t>256786</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>30,19%</t>
+          <t>29,6%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>37,43%</t>
+          <t>37,08%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>308653</t>
+          <t>306155</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>352025</t>
+          <t>348534</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>65,35%</t>
+          <t>64,82%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>74,53%</t>
+          <t>73,79%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>115880</t>
+          <t>115220</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>142967</t>
+          <t>144119</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>52,64%</t>
+          <t>52,34%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>64,95%</t>
+          <t>65,47%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>433268</t>
+          <t>435641</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>483381</t>
+          <t>487463</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>62,57%</t>
+          <t>62,92%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>69,81%</t>
+          <t>70,4%</t>
         </is>
       </c>
     </row>
@@ -2141,7 +2141,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si su trabajo le afecta de manera que tiene dolores de cabeza en 2012</t>
+          <t>Población según si su trabajo le afecta de manera que tiene dolores de cabeza en 2012 (tasa de respuesta: 98,64%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2336,12 +2336,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4832</t>
+          <t>4750</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>16021</t>
+          <t>16486</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2351,12 +2351,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>8,53%</t>
+          <t>8,38%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>28,27%</t>
+          <t>29,09%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>6244</t>
+          <t>6198</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>17644</t>
+          <t>17854</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2386,12 +2386,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>16,46%</t>
+          <t>16,34%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>46,51%</t>
+          <t>47,06%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>13396</t>
+          <t>14118</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>29826</t>
+          <t>29788</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>14,16%</t>
+          <t>14,92%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>31,53%</t>
+          <t>31,48%</t>
         </is>
       </c>
     </row>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>40655</t>
+          <t>40190</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>51844</t>
+          <t>51926</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2464,12 +2464,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>71,73%</t>
+          <t>70,91%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>91,47%</t>
+          <t>91,62%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>20291</t>
+          <t>20081</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>31691</t>
+          <t>31737</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>53,49%</t>
+          <t>52,94%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>83,54%</t>
+          <t>83,66%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>64784</t>
+          <t>64822</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>81214</t>
+          <t>80492</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>68,47%</t>
+          <t>68,52%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>85,84%</t>
+          <t>85,08%</t>
         </is>
       </c>
     </row>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>50035</t>
+          <t>51029</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>78874</t>
+          <t>79112</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>22,58%</t>
+          <t>23,03%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>35,59%</t>
+          <t>35,7%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>43564</t>
+          <t>43624</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>67248</t>
+          <t>67380</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>33,36%</t>
+          <t>33,41%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>51,5%</t>
+          <t>51,6%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>100654</t>
+          <t>102504</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>139113</t>
+          <t>136610</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>28,58%</t>
+          <t>29,1%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>39,5%</t>
+          <t>38,79%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>142750</t>
+          <t>142512</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>171589</t>
+          <t>170595</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>64,41%</t>
+          <t>64,3%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>77,42%</t>
+          <t>76,97%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>63331</t>
+          <t>63199</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>87015</t>
+          <t>86955</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>48,5%</t>
+          <t>48,4%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>66,64%</t>
+          <t>66,59%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>213090</t>
+          <t>215593</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>251549</t>
+          <t>249699</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>60,5%</t>
+          <t>61,21%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>71,42%</t>
+          <t>70,9%</t>
         </is>
       </c>
     </row>
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>6117</t>
+          <t>6142</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>17408</t>
+          <t>18010</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>13,27%</t>
+          <t>13,33%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>37,77%</t>
+          <t>39,08%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>14020</t>
+          <t>13820</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>28508</t>
+          <t>27782</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>30,27%</t>
+          <t>29,83%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>61,54%</t>
+          <t>59,98%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>23083</t>
+          <t>24440</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>43749</t>
+          <t>43125</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>24,98%</t>
+          <t>26,45%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>47,34%</t>
+          <t>46,67%</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>28681</t>
+          <t>28079</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>39972</t>
+          <t>39947</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>62,23%</t>
+          <t>60,92%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>86,73%</t>
+          <t>86,67%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>17813</t>
+          <t>18539</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>32301</t>
+          <t>32501</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>38,46%</t>
+          <t>40,02%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>69,73%</t>
+          <t>70,17%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>48661</t>
+          <t>49285</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>69327</t>
+          <t>67970</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>52,66%</t>
+          <t>53,33%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>75,02%</t>
+          <t>73,55%</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>68702</t>
+          <t>69460</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>100816</t>
+          <t>101574</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>21,18%</t>
+          <t>21,41%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>31,08%</t>
+          <t>31,31%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>74043</t>
+          <t>72440</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>103828</t>
+          <t>103677</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>34,47%</t>
+          <t>33,72%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>48,33%</t>
+          <t>48,26%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>152526</t>
+          <t>151276</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>195686</t>
+          <t>196280</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>28,29%</t>
+          <t>28,05%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>36,29%</t>
+          <t>36,4%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>223572</t>
+          <t>222814</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>255686</t>
+          <t>254928</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>68,92%</t>
+          <t>68,69%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>78,82%</t>
+          <t>78,59%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>111007</t>
+          <t>111158</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>140792</t>
+          <t>142395</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>51,67%</t>
+          <t>51,74%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>65,53%</t>
+          <t>66,28%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>343538</t>
+          <t>342944</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>386698</t>
+          <t>387948</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>63,71%</t>
+          <t>63,6%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>71,71%</t>
+          <t>71,95%</t>
         </is>
       </c>
     </row>
@@ -3744,7 +3744,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si su trabajo le afecta de manera que tiene dolores de cabeza en 2016</t>
+          <t>Población según si su trabajo le afecta de manera que tiene dolores de cabeza en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3939,12 +3939,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6230</t>
+          <t>5954</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>18493</t>
+          <t>18967</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3954,12 +3954,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>11,21%</t>
+          <t>10,71%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>33,27%</t>
+          <t>34,12%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3974,12 +3974,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3995</t>
+          <t>3979</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>12166</t>
+          <t>11991</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3989,12 +3989,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>22,17%</t>
+          <t>22,07%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>67,5%</t>
+          <t>66,53%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>12278</t>
+          <t>12495</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>28416</t>
+          <t>27635</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>16,68%</t>
+          <t>16,98%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>38,61%</t>
+          <t>37,54%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>37088</t>
+          <t>36614</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>49351</t>
+          <t>49627</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>66,73%</t>
+          <t>65,88%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>88,79%</t>
+          <t>89,29%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>5858</t>
+          <t>6033</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>14029</t>
+          <t>14045</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>32,5%</t>
+          <t>33,47%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>77,83%</t>
+          <t>77,93%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>45189</t>
+          <t>45970</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>61327</t>
+          <t>61110</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>61,39%</t>
+          <t>62,46%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>83,32%</t>
+          <t>83,02%</t>
         </is>
       </c>
     </row>
@@ -4282,12 +4282,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>48323</t>
+          <t>46906</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>74713</t>
+          <t>73789</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4297,12 +4297,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>21,07%</t>
+          <t>20,45%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>32,57%</t>
+          <t>32,17%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>44744</t>
+          <t>44985</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>66699</t>
+          <t>66352</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4332,12 +4332,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>35,92%</t>
+          <t>36,11%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>53,55%</t>
+          <t>53,27%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>98309</t>
+          <t>97475</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>134089</t>
+          <t>132799</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>27,77%</t>
+          <t>27,54%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>37,88%</t>
+          <t>37,52%</t>
         </is>
       </c>
     </row>
@@ -4395,12 +4395,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>154669</t>
+          <t>155593</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>181059</t>
+          <t>182476</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>67,43%</t>
+          <t>67,83%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>78,93%</t>
+          <t>79,55%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>57866</t>
+          <t>58213</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>79821</t>
+          <t>79580</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>46,45%</t>
+          <t>46,73%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>64,08%</t>
+          <t>63,89%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>219858</t>
+          <t>221148</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>255638</t>
+          <t>256472</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>62,12%</t>
+          <t>62,48%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>72,23%</t>
+          <t>72,46%</t>
         </is>
       </c>
     </row>
@@ -4625,12 +4625,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>14346</t>
+          <t>14238</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>30383</t>
+          <t>29959</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4640,12 +4640,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>22,58%</t>
+          <t>22,41%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>47,83%</t>
+          <t>47,16%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4660,12 +4660,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>18909</t>
+          <t>18795</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>35942</t>
+          <t>35730</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4675,12 +4675,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>25,65%</t>
+          <t>25,5%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>48,76%</t>
+          <t>48,47%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>36648</t>
+          <t>36938</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>60466</t>
+          <t>60883</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>26,7%</t>
+          <t>26,92%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>44,06%</t>
+          <t>44,36%</t>
         </is>
       </c>
     </row>
@@ -4738,12 +4738,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>33145</t>
+          <t>33569</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>49182</t>
+          <t>49290</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>52,17%</t>
+          <t>52,84%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>77,42%</t>
+          <t>77,59%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4773,12 +4773,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>37766</t>
+          <t>37978</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>54799</t>
+          <t>54913</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>51,24%</t>
+          <t>51,53%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>74,35%</t>
+          <t>74,5%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>76770</t>
+          <t>76353</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>100588</t>
+          <t>100298</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>55,94%</t>
+          <t>55,64%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>73,3%</t>
+          <t>73,08%</t>
         </is>
       </c>
     </row>
@@ -4968,12 +4968,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>77573</t>
+          <t>75845</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>113483</t>
+          <t>109860</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4983,12 +4983,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>22,26%</t>
+          <t>21,76%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>32,56%</t>
+          <t>31,52%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5003,12 +5003,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>75682</t>
+          <t>74529</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>104613</t>
+          <t>104549</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5018,12 +5018,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>34,99%</t>
+          <t>34,46%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>48,37%</t>
+          <t>48,34%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>159653</t>
+          <t>161740</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>207816</t>
+          <t>206875</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>28,27%</t>
+          <t>28,64%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>36,8%</t>
+          <t>36,63%</t>
         </is>
       </c>
     </row>
@@ -5081,12 +5081,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>235008</t>
+          <t>238631</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>270918</t>
+          <t>272646</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>67,44%</t>
+          <t>68,48%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>77,74%</t>
+          <t>78,24%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>111685</t>
+          <t>111749</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>140616</t>
+          <t>141769</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>51,63%</t>
+          <t>51,66%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>65,01%</t>
+          <t>65,54%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>356972</t>
+          <t>357913</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>405135</t>
+          <t>403048</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>63,2%</t>
+          <t>63,37%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>71,73%</t>
+          <t>71,36%</t>
         </is>
       </c>
     </row>
@@ -5347,7 +5347,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si su trabajo le afecta de manera que tiene dolores de cabeza en 2023</t>
+          <t>Población según si su trabajo le afecta de manera que tiene dolores de cabeza en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5542,12 +5542,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>173</t>
+          <t>175</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>10227</t>
+          <t>10359</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5557,12 +5557,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>35,01%</t>
+          <t>35,46%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>5615</t>
+          <t>5801</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>18984</t>
+          <t>18721</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5592,12 +5592,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>22,47%</t>
+          <t>23,22%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>75,98%</t>
+          <t>74,93%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5612,12 +5612,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>6521</t>
+          <t>6995</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>25455</t>
+          <t>26981</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5627,12 +5627,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>12,03%</t>
+          <t>12,91%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>46,97%</t>
+          <t>49,78%</t>
         </is>
       </c>
     </row>
@@ -5655,12 +5655,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>18987</t>
+          <t>18855</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>29041</t>
+          <t>29039</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5670,12 +5670,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>64,99%</t>
+          <t>64,54%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,41%</t>
+          <t>99,4%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5690,12 +5690,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>6002</t>
+          <t>6265</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>19371</t>
+          <t>19185</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5705,12 +5705,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>24,02%</t>
+          <t>25,07%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>77,53%</t>
+          <t>76,78%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>28745</t>
+          <t>27219</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>47679</t>
+          <t>47205</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5740,12 +5740,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>53,03%</t>
+          <t>50,22%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>87,97%</t>
+          <t>87,09%</t>
         </is>
       </c>
     </row>
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>37185</t>
+          <t>37956</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>64062</t>
+          <t>65368</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5900,12 +5900,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>15,52%</t>
+          <t>15,84%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>26,74%</t>
+          <t>27,28%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>39422</t>
+          <t>39354</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>81306</t>
+          <t>81408</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5935,12 +5935,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>16,54%</t>
+          <t>16,51%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>34,11%</t>
+          <t>34,15%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5955,12 +5955,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>89324</t>
+          <t>89767</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>135057</t>
+          <t>136234</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5970,12 +5970,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>18,69%</t>
+          <t>18,78%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>28,26%</t>
+          <t>28,5%</t>
         </is>
       </c>
     </row>
@@ -5998,12 +5998,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>175518</t>
+          <t>174212</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>202395</t>
+          <t>201624</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>73,26%</t>
+          <t>72,72%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>84,48%</t>
+          <t>84,16%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>157062</t>
+          <t>156960</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>198946</t>
+          <t>199014</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>65,89%</t>
+          <t>65,85%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>83,46%</t>
+          <t>83,49%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>342891</t>
+          <t>341714</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>388624</t>
+          <t>388181</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6083,12 +6083,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>71,74%</t>
+          <t>71,5%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>81,31%</t>
+          <t>81,22%</t>
         </is>
       </c>
     </row>
@@ -6228,12 +6228,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>16529</t>
+          <t>15353</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>35791</t>
+          <t>34909</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6243,12 +6243,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>23,77%</t>
+          <t>22,08%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>51,48%</t>
+          <t>50,21%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6263,12 +6263,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>30094</t>
+          <t>29961</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>46667</t>
+          <t>47088</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6278,12 +6278,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>33,18%</t>
+          <t>33,03%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>51,45%</t>
+          <t>51,92%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6298,12 +6298,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>51107</t>
+          <t>50267</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>76302</t>
+          <t>76352</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6313,12 +6313,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>31,9%</t>
+          <t>31,37%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>47,62%</t>
+          <t>47,65%</t>
         </is>
       </c>
     </row>
@@ -6341,12 +6341,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>33735</t>
+          <t>34617</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>52997</t>
+          <t>54173</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6356,12 +6356,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>48,52%</t>
+          <t>49,79%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>76,23%</t>
+          <t>77,92%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6376,12 +6376,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>44028</t>
+          <t>43607</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>60601</t>
+          <t>60734</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6391,12 +6391,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>48,55%</t>
+          <t>48,08%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>66,82%</t>
+          <t>66,97%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6411,12 +6411,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>83919</t>
+          <t>83869</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>109114</t>
+          <t>109954</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6426,12 +6426,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>52,38%</t>
+          <t>52,35%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>68,1%</t>
+          <t>68,63%</t>
         </is>
       </c>
     </row>
@@ -6571,12 +6571,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>62190</t>
+          <t>60384</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>97009</t>
+          <t>96202</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6586,12 +6586,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>18,38%</t>
+          <t>17,85%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>28,67%</t>
+          <t>28,44%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6606,12 +6606,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>84856</t>
+          <t>84380</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>135961</t>
+          <t>134923</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6621,12 +6621,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>23,97%</t>
+          <t>23,83%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>38,4%</t>
+          <t>38,11%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6641,12 +6641,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>159303</t>
+          <t>152827</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>220290</t>
+          <t>218611</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6656,12 +6656,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>23,01%</t>
+          <t>22,07%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>31,82%</t>
+          <t>31,57%</t>
         </is>
       </c>
     </row>
@@ -6684,12 +6684,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>241311</t>
+          <t>242118</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>276130</t>
+          <t>277936</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6699,12 +6699,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>71,33%</t>
+          <t>71,56%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>81,62%</t>
+          <t>82,15%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6719,12 +6719,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>218088</t>
+          <t>219126</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>269193</t>
+          <t>269669</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6734,12 +6734,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>61,6%</t>
+          <t>61,89%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>76,03%</t>
+          <t>76,17%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6754,12 +6754,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>472079</t>
+          <t>473758</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>533066</t>
+          <t>539542</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6769,12 +6769,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>68,18%</t>
+          <t>68,43%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>76,99%</t>
+          <t>77,93%</t>
         </is>
       </c>
     </row>
